--- a/output/pdf_financials_xlsx/SPD.xlsx
+++ b/output/pdf_financials_xlsx/SPD.xlsx
@@ -5427,25 +5427,25 @@
         <v>0.178982</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.412211</v>
+        <v>0.178982</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.954638</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.438812</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.644349</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.697311</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.702052</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.723832</v>
       </c>
       <c r="K92" s="1" t="inlineStr">
         <is>
@@ -5453,16 +5453,16 @@
         </is>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.807426</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.988701</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.988701</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.988701</v>
       </c>
     </row>
     <row r="93">
@@ -8842,7 +8842,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10390,7 +10394,11 @@
           <t>Reserves 2,804,147</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -11886,7 +11894,11 @@
           <t>Reserves 2,750,223</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -13472,7 +13484,11 @@
           <t>Reserves 2,723,832</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -15204,7 +15220,11 @@
           <t>Reserves 2,702,052</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -16790,7 +16810,11 @@
           <t>Reserves 2,697,311</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -18258,7 +18282,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -20334,7 +20362,11 @@
           <t>Reserves 1,954,638</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -47314,7 +47346,7 @@
         </is>
       </c>
       <c r="E461" s="5" t="n">
-        <v>0.122498</v>
+        <v>-0.122498</v>
       </c>
       <c r="F461" s="5" t="n">
         <v>-0.306392</v>

--- a/output/pdf_financials_xlsx/SPD.xlsx
+++ b/output/pdf_financials_xlsx/SPD.xlsx
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.006076</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004443</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.06949900000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005479</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.352888</v>
+        <v>-0.358964</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.300635</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.548925</v>
+        <v>-1.553368</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.44944</v>
+        <v>-5.518939</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.177636</v>
+        <v>-5.183115</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-9.325843000000001</v>
@@ -2000,19 +2000,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.352888</v>
+        <v>-0.358964</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.300635</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.548925</v>
+        <v>-1.553368</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.44944</v>
+        <v>-5.518939</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.177636</v>
+        <v>-5.183115</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-9.325843000000001</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.8584</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.065276</v>
@@ -2296,10 +2296,10 @@
         <v>0.552675</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.027401</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.364139</v>
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.15175</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.152901</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0.974</v>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.8584</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.065276</v>
@@ -2398,10 +2398,10 @@
         <v>0.552675</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.027401</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.364139</v>
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.15175</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.025</v>
+        <v>0.177901</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0.974</v>
@@ -2989,7 +2989,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.431538</v>
+        <v>1.573138</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.778626</v>
@@ -3010,10 +3010,10 @@
         <v>0.973526</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>6.84092</v>
+        <v>6.813519</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.672719</v>
+        <v>5.30858</v>
       </c>
       <c r="K48" s="1" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.205494</v>
+        <v>0.053744</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.334319</v>
+        <v>2.181418</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.5048280000000001</v>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -44774,7 +44774,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E431" s="5" t="n">
